--- a/data/DatasetS6.xlsx
+++ b/data/DatasetS6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\Postdoc1\supplementary_information\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\Postdoc1\ECCO-dataset\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62950AF-860E-41EC-B3D9-37D1C053FF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242D5E5B-FCCC-45FD-A237-A2BE856CE5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{514D0FF8-3D39-4E86-9FD3-668A103A003A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{514D0FF8-3D39-4E86-9FD3-668A103A003A}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -956,22 +956,22 @@
         <v>6000</v>
       </c>
       <c r="G2" s="5">
-        <v>0.15084839999999999</v>
+        <v>0.16049811497745101</v>
       </c>
       <c r="H2" s="5">
-        <v>-0.44345960000000001</v>
+        <v>-0.45786095507368002</v>
       </c>
       <c r="I2" s="5">
-        <v>0.32390419999999998</v>
+        <v>0.32390417372368302</v>
       </c>
       <c r="J2" s="5">
-        <v>0.33002920000000002</v>
+        <v>0.330029225468913</v>
       </c>
       <c r="K2" s="5">
-        <v>0.59377690000000005</v>
+        <v>0.59377686418981201</v>
       </c>
       <c r="L2" s="5">
-        <v>0.78780300000000003</v>
+        <v>0.78780297318687198</v>
       </c>
       <c r="M2" s="5">
         <v>11</v>
@@ -1006,22 +1006,22 @@
         <v>3000</v>
       </c>
       <c r="G3" s="5">
-        <v>-0.8610257</v>
+        <v>-0.85057345246106797</v>
       </c>
       <c r="H3" s="5">
-        <v>-3.6680679999999999</v>
+        <v>-3.7012936072586302</v>
       </c>
       <c r="I3" s="5">
-        <v>-0.55004189999999997</v>
+        <v>-0.55004190012544596</v>
       </c>
       <c r="J3" s="5">
-        <v>-3.524826</v>
+        <v>-3.5248261091806898</v>
       </c>
       <c r="K3" s="5">
-        <v>-0.89800619999999998</v>
+        <v>-0.89800622599487501</v>
       </c>
       <c r="L3" s="5">
-        <v>-3.424293</v>
+        <v>-3.42429253544028</v>
       </c>
       <c r="M3" s="5">
         <v>13</v>
@@ -1056,22 +1056,22 @@
         <v>3000</v>
       </c>
       <c r="G4" s="5">
-        <v>1.130889</v>
+        <v>1.10634642587971</v>
       </c>
       <c r="H4" s="5">
-        <v>-2.50005275</v>
+        <v>-2.5205246923667626</v>
       </c>
       <c r="I4" s="5">
-        <v>1.1733677499999999</v>
+        <v>1.173367622197905</v>
       </c>
       <c r="J4" s="5">
-        <v>-2.5510354999999998</v>
+        <v>-2.5510352172163175</v>
       </c>
       <c r="K4" s="5">
-        <v>0.9728348</v>
+        <v>0.97283477344154601</v>
       </c>
       <c r="L4" s="5">
-        <v>-2.3512312500000001</v>
+        <v>-2.3512310952079849</v>
       </c>
       <c r="M4" s="5">
         <v>16</v>
@@ -1106,22 +1106,22 @@
         <v>1280</v>
       </c>
       <c r="G5" s="5">
-        <v>-0.18530930000000001</v>
+        <v>-0.20110100356264399</v>
       </c>
       <c r="H5" s="5">
-        <v>-3.0092479999999999</v>
+        <v>-3.0349285334200999</v>
       </c>
       <c r="I5" s="5">
-        <v>-0.35828389999999999</v>
+        <v>-0.27601828535848599</v>
       </c>
       <c r="J5" s="5">
-        <v>-3.0680399999999999</v>
+        <v>-3.0470109215578054</v>
       </c>
       <c r="K5" s="5">
-        <v>-0.35828389999999999</v>
+        <v>-0.35828392676462301</v>
       </c>
       <c r="L5" s="5">
-        <v>-3.0680399999999999</v>
+        <v>-3.0680404462585802</v>
       </c>
       <c r="M5" s="5">
         <v>11</v>
@@ -1156,22 +1156,22 @@
         <v>3000</v>
       </c>
       <c r="G6" s="5">
-        <v>0.46948410000000002</v>
+        <v>0.46703781283648599</v>
       </c>
       <c r="H6" s="5">
-        <v>-0.78570850000000003</v>
+        <v>-0.80313959384974798</v>
       </c>
       <c r="I6" s="5">
-        <v>0.60714170000000001</v>
+        <v>0.60714167495402505</v>
       </c>
       <c r="J6" s="5">
-        <v>-0.6014912</v>
+        <v>-0.60149118611664298</v>
       </c>
       <c r="K6" s="5">
-        <v>0.13617080000000001</v>
+        <v>0.13617078759024501</v>
       </c>
       <c r="L6" s="5">
-        <v>-0.54139130000000002</v>
+        <v>-0.54139130112612299</v>
       </c>
       <c r="M6" s="5">
         <v>9</v>
@@ -1206,22 +1206,22 @@
         <v>5650</v>
       </c>
       <c r="G7" s="5">
-        <v>-9.6256380000000002E-2</v>
+        <v>-0.29210487696402132</v>
       </c>
       <c r="H7" s="5">
-        <v>-2.8675160000000002</v>
+        <v>-3.1406007365142399</v>
       </c>
       <c r="I7" s="5">
-        <v>0.1808797</v>
+        <v>-4.3615362882057002E-2</v>
       </c>
       <c r="J7" s="5">
-        <v>-3.0150111000000002</v>
+        <v>-3.2515714602688552</v>
       </c>
       <c r="K7" s="5">
-        <v>7.0269709999999999E-2</v>
+        <v>-0.1206686815827494</v>
       </c>
       <c r="L7" s="5">
-        <v>-2.846768</v>
+        <v>-3.10941415952558</v>
       </c>
       <c r="M7" s="5">
         <v>12</v>
@@ -1256,22 +1256,22 @@
         <v>5000</v>
       </c>
       <c r="G8" s="5">
-        <v>-0.88981034999999997</v>
+        <v>-0.88029916265735308</v>
       </c>
       <c r="H8" s="5">
-        <v>0.38727309999999998</v>
+        <v>0.36120325289080751</v>
       </c>
       <c r="I8" s="5">
-        <v>-0.46287495000000001</v>
+        <v>-0.46287493927116852</v>
       </c>
       <c r="J8" s="5">
-        <v>0.70085529999999996</v>
+        <v>0.70085530675577457</v>
       </c>
       <c r="K8" s="5">
-        <v>-0.59661474999999997</v>
+        <v>-0.5966147473830995</v>
       </c>
       <c r="L8" s="5">
-        <v>0.81607015000000005</v>
+        <v>0.81607011611543601</v>
       </c>
       <c r="M8" s="5">
         <v>11</v>
@@ -1306,22 +1306,22 @@
         <v>3500</v>
       </c>
       <c r="G9" s="5">
-        <v>2.4325085</v>
+        <v>2.4503170933883598</v>
       </c>
       <c r="H9" s="5">
-        <v>-1.536351</v>
+        <v>-1.5062143905209924</v>
       </c>
       <c r="I9" s="5">
-        <v>2.5974854999999999</v>
+        <v>2.5974854707083699</v>
       </c>
       <c r="J9" s="5">
-        <v>-1.3776014999999999</v>
+        <v>-1.377601386714125</v>
       </c>
       <c r="K9" s="5">
-        <v>2.283836</v>
+        <v>2.2838363195421101</v>
       </c>
       <c r="L9" s="5">
-        <v>-1.5817895</v>
+        <v>-1.58178952009643</v>
       </c>
       <c r="M9" s="5">
         <v>18</v>
@@ -1356,22 +1356,22 @@
         <v>8950</v>
       </c>
       <c r="G10" s="5">
-        <v>6.6004940000000003</v>
+        <v>6.5949255133653901</v>
       </c>
       <c r="H10" s="5">
-        <v>3.7856269999999999</v>
+        <v>3.7870664803779901</v>
       </c>
       <c r="I10" s="5">
-        <v>6.2668429999999997</v>
+        <v>6.2668425423981304</v>
       </c>
       <c r="J10" s="5">
-        <v>3.9843350000000002</v>
+        <v>3.98433497235983</v>
       </c>
       <c r="K10" s="5">
-        <v>6.2668429999999997</v>
+        <v>6.2668425423981304</v>
       </c>
       <c r="L10" s="5">
-        <v>3.9843350000000002</v>
+        <v>3.98433497235983</v>
       </c>
       <c r="M10" s="5">
         <v>15</v>
@@ -1406,22 +1406,22 @@
         <v>3000</v>
       </c>
       <c r="G11" s="5">
-        <v>-0.8610257</v>
+        <v>-0.85057345246106797</v>
       </c>
       <c r="H11" s="5">
-        <v>-3.6680679999999999</v>
+        <v>-3.7012936072586302</v>
       </c>
       <c r="I11" s="5">
-        <v>-0.55004189999999997</v>
+        <v>-0.55004190012544596</v>
       </c>
       <c r="J11" s="5">
-        <v>-3.524826</v>
+        <v>-3.5248261091806898</v>
       </c>
       <c r="K11" s="5">
-        <v>-0.89800619999999998</v>
+        <v>-0.89800622599487501</v>
       </c>
       <c r="L11" s="5">
-        <v>-3.424293</v>
+        <v>-3.42429253544028</v>
       </c>
       <c r="M11" s="5">
         <v>13</v>
@@ -1456,22 +1456,22 @@
         <v>5000</v>
       </c>
       <c r="G12" s="5">
-        <v>-3.7829475000000001</v>
+        <v>-3.7753033456518548</v>
       </c>
       <c r="H12" s="5">
-        <v>-0.72105850000000005</v>
+        <v>-0.77330350480000343</v>
       </c>
       <c r="I12" s="5">
-        <v>-3.7496070000000001</v>
+        <v>-3.4350513224170252</v>
       </c>
       <c r="J12" s="5">
-        <v>-0.3259261</v>
+        <v>-0.588254532921616</v>
       </c>
       <c r="K12" s="5">
-        <v>-3.7910119999999998</v>
+        <v>-3.4295731785580399</v>
       </c>
       <c r="L12" s="5">
-        <v>0.40405400000000002</v>
+        <v>6.4771541691474976E-2</v>
       </c>
       <c r="M12" s="5">
         <v>11</v>
@@ -1506,22 +1506,22 @@
         <v>3500</v>
       </c>
       <c r="G13" s="5">
-        <v>2.4279250000000001</v>
+        <v>2.4222754559584798</v>
       </c>
       <c r="H13" s="5">
-        <v>-2.579183</v>
+        <v>-2.5826523054159303</v>
       </c>
       <c r="I13" s="5">
-        <v>2.4657450000000001</v>
+        <v>2.46574457165794</v>
       </c>
       <c r="J13" s="5">
-        <v>-2.6226880000000001</v>
+        <v>-2.6226881690436099</v>
       </c>
       <c r="K13" s="5">
-        <v>2.4847410000000001</v>
+        <v>2.4847409932223998</v>
       </c>
       <c r="L13" s="5">
-        <v>-2.3245779999999998</v>
+        <v>-2.3245775556767798</v>
       </c>
       <c r="M13" s="5">
         <v>14</v>
@@ -1556,22 +1556,22 @@
         <v>6500</v>
       </c>
       <c r="G14" s="5">
-        <v>4.7417730000000002</v>
+        <v>4.7503649518251301</v>
       </c>
       <c r="H14" s="5">
-        <v>0.88437220000000005</v>
+        <v>0.92968356057820145</v>
       </c>
       <c r="I14" s="5">
-        <v>4.9737900000000002</v>
+        <v>4.9737900654575302</v>
       </c>
       <c r="J14" s="5">
-        <v>1.459438</v>
+        <v>1.4594379661572501</v>
       </c>
       <c r="K14" s="5">
-        <v>4.9350820000000004</v>
+        <v>4.9350819723747303</v>
       </c>
       <c r="L14" s="5">
-        <v>1.5356669999999999</v>
+        <v>1.5356667247956699</v>
       </c>
       <c r="M14" s="5">
         <v>11</v>
@@ -1606,22 +1606,22 @@
         <v>3500</v>
       </c>
       <c r="G15" s="5">
-        <v>1.5873170000000001</v>
+        <v>1.6643888277588599</v>
       </c>
       <c r="H15" s="5">
-        <v>-1.9846969999999999</v>
+        <v>-1.93814396153506</v>
       </c>
       <c r="I15" s="5">
-        <v>1.8370124999999999</v>
+        <v>1.837012579998635</v>
       </c>
       <c r="J15" s="5">
-        <v>-1.7951094999999999</v>
+        <v>-1.7951093596079799</v>
       </c>
       <c r="K15" s="5">
-        <v>1.729203</v>
+        <v>1.729203250727515</v>
       </c>
       <c r="L15" s="5">
-        <v>-1.6577115</v>
+        <v>-1.6577118193395148</v>
       </c>
       <c r="M15" s="5">
         <v>11</v>
@@ -1656,22 +1656,22 @@
         <v>3000</v>
       </c>
       <c r="G16" s="5">
-        <v>-2.4082539999999999</v>
+        <v>-2.3851031341671698</v>
       </c>
       <c r="H16" s="5">
-        <v>-2.227338</v>
+        <v>-2.2489235569186898</v>
       </c>
       <c r="I16" s="5">
-        <v>-2.4636300000000002</v>
+        <v>-2.4636300183915698</v>
       </c>
       <c r="J16" s="5">
-        <v>-2.2122160000000002</v>
+        <v>-2.2122161677197898</v>
       </c>
       <c r="K16" s="5">
-        <v>-2.65802</v>
+        <v>-2.6580196344606701</v>
       </c>
       <c r="L16" s="5">
-        <v>-2.23569</v>
+        <v>-2.2356901374752098</v>
       </c>
       <c r="M16" s="5">
         <v>8</v>
@@ -1706,22 +1706,22 @@
         <v>5650</v>
       </c>
       <c r="G17" s="5">
-        <v>0.21568979999999999</v>
+        <v>0.205901841168003</v>
       </c>
       <c r="H17" s="5">
-        <v>-2.486866</v>
+        <v>-2.6222843070308999</v>
       </c>
       <c r="I17" s="5">
-        <v>0.54488970000000003</v>
+        <v>0.54488967728431204</v>
       </c>
       <c r="J17" s="5">
-        <v>-2.688987</v>
+        <v>-2.68898743522755</v>
       </c>
       <c r="K17" s="5">
-        <v>0.2059018</v>
+        <v>0.205901841168003</v>
       </c>
       <c r="L17" s="5">
-        <v>-2.6222840000000001</v>
+        <v>-2.6222843070308999</v>
       </c>
       <c r="M17" s="5">
         <v>12</v>
@@ -1756,22 +1756,22 @@
         <v>4000</v>
       </c>
       <c r="G18" s="5">
-        <v>0.22636314799999999</v>
+        <v>0.22916195488284541</v>
       </c>
       <c r="H18" s="5">
-        <v>-0.21636662500000001</v>
+        <v>-0.23080377917770953</v>
       </c>
       <c r="I18" s="5">
-        <v>-6.0696343E-2</v>
+        <v>3.8143855595010677E-2</v>
       </c>
       <c r="J18" s="5">
-        <v>-0.32256050000000003</v>
+        <v>-0.18495811101337048</v>
       </c>
       <c r="K18" s="5">
-        <v>-0.14873286699999999</v>
+        <v>-4.1322620717685749E-2</v>
       </c>
       <c r="L18" s="5">
-        <v>-0.2083305</v>
+        <v>-4.8496615310305489E-2</v>
       </c>
       <c r="M18" s="5">
         <v>9</v>
@@ -1806,22 +1806,22 @@
         <v>6000</v>
       </c>
       <c r="G19" s="5">
-        <v>-0.35701739999999998</v>
+        <v>-0.34649245988663602</v>
       </c>
       <c r="H19" s="5">
-        <v>-2.0476610000000002</v>
+        <v>-2.0541914922944802</v>
       </c>
       <c r="I19" s="5">
-        <v>0.18655820000000001</v>
+        <v>0.186558212319066</v>
       </c>
       <c r="J19" s="5">
-        <v>-1.91845</v>
+        <v>-1.9184496818323</v>
       </c>
       <c r="K19" s="5">
-        <v>0.21582270000000001</v>
+        <v>0.21582265093946401</v>
       </c>
       <c r="L19" s="5">
-        <v>-1.838538</v>
+        <v>-1.83853811201522</v>
       </c>
       <c r="M19" s="5">
         <v>14</v>
@@ -1856,22 +1856,22 @@
         <v>3000</v>
       </c>
       <c r="G20" s="5">
-        <v>-0.62644739999999999</v>
+        <v>-0.61711093830599695</v>
       </c>
       <c r="H20" s="5">
-        <v>-2.0614180000000002</v>
+        <v>-2.0776652323537599</v>
       </c>
       <c r="I20" s="5">
-        <v>-0.28602499999999997</v>
+        <v>-0.28602495565309499</v>
       </c>
       <c r="J20" s="5">
-        <v>-1.864293</v>
+        <v>-1.86429285251557</v>
       </c>
       <c r="K20" s="5">
-        <v>-0.13959289999999999</v>
+        <v>-0.139592949317801</v>
       </c>
       <c r="L20" s="5">
-        <v>-1.8605590000000001</v>
+        <v>-1.8605594786736499</v>
       </c>
       <c r="M20" s="5">
         <v>13</v>
@@ -1906,22 +1906,22 @@
         <v>4000</v>
       </c>
       <c r="G21" s="5">
-        <v>-2.3382689999999999</v>
+        <v>-2.3184483935461402</v>
       </c>
       <c r="H21" s="5">
-        <v>-1.7989170000000001</v>
+        <v>-1.8168993097100801</v>
       </c>
       <c r="I21" s="5">
-        <v>-2.3860640000000002</v>
+        <v>-2.3860636018161601</v>
       </c>
       <c r="J21" s="5">
-        <v>-1.656007</v>
+        <v>-1.6560072410520299</v>
       </c>
       <c r="K21" s="5">
-        <v>-2.4034230000000001</v>
+        <v>-2.4034227663935801</v>
       </c>
       <c r="L21" s="5">
-        <v>-1.7046190000000001</v>
+        <v>-1.7046193313962399</v>
       </c>
       <c r="M21" s="5">
         <v>8</v>
@@ -1956,22 +1956,22 @@
         <v>2000</v>
       </c>
       <c r="G22" s="5">
-        <v>0.72892409999999996</v>
+        <v>0.74298166738498606</v>
       </c>
       <c r="H22" s="5">
-        <v>0.60426849999999999</v>
+        <v>0.593756972983426</v>
       </c>
       <c r="I22" s="5">
-        <v>0.87397610000000003</v>
+        <v>0.87397614181858196</v>
       </c>
       <c r="J22" s="5">
-        <v>0.66569279999999997</v>
+        <v>0.66569276660858401</v>
       </c>
       <c r="K22" s="5">
-        <v>2.5336370000000001</v>
+        <v>2.53363741437028</v>
       </c>
       <c r="L22" s="5">
-        <v>2.387076</v>
+        <v>2.3870760438102199</v>
       </c>
       <c r="M22" s="5">
         <v>16</v>
@@ -2006,22 +2006,22 @@
         <v>4000</v>
       </c>
       <c r="G23" s="5">
-        <v>-2.4833430000000001</v>
+        <v>-2.4182734180932299</v>
       </c>
       <c r="H23" s="5">
-        <v>-1.3654028499999999</v>
+        <v>-1.0007253514296901</v>
       </c>
       <c r="I23" s="5">
-        <v>-2.4016799999999998</v>
+        <v>-2.36350913406427</v>
       </c>
       <c r="J23" s="5">
-        <v>-1.22410435</v>
+        <v>-0.85264779247372602</v>
       </c>
       <c r="K23" s="5">
-        <v>-2.2743324999999999</v>
+        <v>-2.1232295190310499</v>
       </c>
       <c r="L23" s="5">
-        <v>0.12053575</v>
+        <v>0.74536461302603396</v>
       </c>
       <c r="M23" s="5">
         <v>13</v>
@@ -2056,22 +2056,22 @@
         <v>6000</v>
       </c>
       <c r="G24" s="5">
-        <v>3.561788</v>
+        <v>3.56666609163209</v>
       </c>
       <c r="H24" s="5">
-        <v>-0.1859885</v>
+        <v>-0.180176876548618</v>
       </c>
       <c r="I24" s="5">
-        <v>3.0773459999999999</v>
+        <v>3.0773462229395001</v>
       </c>
       <c r="J24" s="5">
-        <v>-0.79791069999999997</v>
+        <v>-0.79791070429522304</v>
       </c>
       <c r="K24" s="5">
-        <v>2.5740189999999998</v>
+        <v>2.5740187880409202</v>
       </c>
       <c r="L24" s="5">
-        <v>-1.4906189999999999</v>
+        <v>-1.4906185534576299</v>
       </c>
       <c r="M24" s="5">
         <v>16</v>
@@ -2106,22 +2106,22 @@
         <v>2500</v>
       </c>
       <c r="G25" s="5">
-        <v>1.4173340000000001</v>
+        <v>1.488743146266305</v>
       </c>
       <c r="H25" s="5">
-        <v>-1.9565589999999999</v>
+        <v>-1.91416852425885</v>
       </c>
       <c r="I25" s="5">
-        <v>1.616325</v>
+        <v>1.6163245773532899</v>
       </c>
       <c r="J25" s="5">
-        <v>-1.7795380000000001</v>
+        <v>-1.7795380507487799</v>
       </c>
       <c r="K25" s="5">
-        <v>1.339772</v>
+        <v>1.3397716930085499</v>
       </c>
       <c r="L25" s="5">
-        <v>-1.8091159999999999</v>
+        <v>-1.8091164221907099</v>
       </c>
       <c r="M25" s="5">
         <v>11</v>
@@ -2156,22 +2156,22 @@
         <v>3000</v>
       </c>
       <c r="G26" s="5">
-        <v>-0.68044420000000005</v>
+        <v>-0.474025689660798</v>
       </c>
       <c r="H26" s="5">
-        <v>-3.5773220000000001</v>
+        <v>-3.7260759179164</v>
       </c>
       <c r="I26" s="5">
-        <v>-0.44971366000000002</v>
+        <v>-0.25201904723348301</v>
       </c>
       <c r="J26" s="5">
-        <v>-3.5836100000000002</v>
+        <v>-3.683774109623895</v>
       </c>
       <c r="K26" s="5">
-        <v>-0.69386519999999996</v>
+        <v>-0.47909830074960702</v>
       </c>
       <c r="L26" s="5">
-        <v>-3.4108459999999998</v>
+        <v>-3.5296816773488953</v>
       </c>
       <c r="M26" s="5">
         <v>13</v>
@@ -2206,22 +2206,22 @@
         <v>3500</v>
       </c>
       <c r="G27" s="5">
-        <v>2.0570369999999998</v>
+        <v>2.1054424988511578</v>
       </c>
       <c r="H27" s="5">
-        <v>-3.8470944999999999</v>
+        <v>-3.8012019960517947</v>
       </c>
       <c r="I27" s="5">
-        <v>2.5252515</v>
+        <v>2.525251827906275</v>
       </c>
       <c r="J27" s="5">
-        <v>-3.2870325</v>
+        <v>-3.2870324949400649</v>
       </c>
       <c r="K27" s="5">
-        <v>1.9350719999999999</v>
+        <v>1.9350720735232052</v>
       </c>
       <c r="L27" s="5">
-        <v>-3.4537740000000001</v>
+        <v>-3.4537742527077548</v>
       </c>
       <c r="M27" s="5">
         <v>17</v>
@@ -2256,22 +2256,22 @@
         <v>6700</v>
       </c>
       <c r="G28" s="5">
-        <v>1.8267450000000001</v>
+        <v>1.81945625254615</v>
       </c>
       <c r="H28" s="5">
-        <v>-2.3644440000000002</v>
+        <v>-2.36011563882162</v>
       </c>
       <c r="I28" s="5">
-        <v>2.4424630000000001</v>
+        <v>2.4424628298909101</v>
       </c>
       <c r="J28" s="5">
-        <v>-2.1239430000000001</v>
+        <v>-2.1239426436172302</v>
       </c>
       <c r="K28" s="5">
-        <v>2.0481189999999998</v>
+        <v>2.0481187601736401</v>
       </c>
       <c r="L28" s="5">
-        <v>-2.2033559999999999</v>
+        <v>-2.2033557677103199</v>
       </c>
       <c r="M28" s="5">
         <v>14</v>
@@ -2306,22 +2306,22 @@
         <v>3480</v>
       </c>
       <c r="G29" s="5">
-        <v>2.4500405000000001</v>
+        <v>2.4160120418140649</v>
       </c>
       <c r="H29" s="5">
-        <v>-0.58946394999999996</v>
+        <v>-0.6068439037446296</v>
       </c>
       <c r="I29" s="5">
-        <v>2.1969815000000001</v>
+        <v>2.321706306269165</v>
       </c>
       <c r="J29" s="5">
-        <v>-0.43152790000000002</v>
+        <v>-0.46437225216444378</v>
       </c>
       <c r="K29" s="5">
-        <v>2.1969815000000001</v>
+        <v>2.1969815349240998</v>
       </c>
       <c r="L29" s="5">
-        <v>-0.43152790000000002</v>
+        <v>-0.431527891118687</v>
       </c>
       <c r="M29" s="5">
         <v>17</v>
@@ -2356,22 +2356,22 @@
         <v>6000</v>
       </c>
       <c r="G30" s="5">
-        <v>0.28660679999999999</v>
+        <v>0.299230770070193</v>
       </c>
       <c r="H30" s="5">
-        <v>-1.5297000000000001</v>
+        <v>-1.53399096972448</v>
       </c>
       <c r="I30" s="5">
-        <v>0.76527800000000001</v>
+        <v>0.76527796637193202</v>
       </c>
       <c r="J30" s="5">
-        <v>-1.2993060000000001</v>
+        <v>-1.2993060475648399</v>
       </c>
       <c r="K30" s="5">
-        <v>0.90141230000000006</v>
+        <v>0.90141228581118704</v>
       </c>
       <c r="L30" s="5">
-        <v>-1.0205420000000001</v>
+        <v>-1.02054177915947</v>
       </c>
       <c r="M30" s="5">
         <v>14</v>
@@ -2406,22 +2406,22 @@
         <v>4000</v>
       </c>
       <c r="G31" s="5">
-        <v>-2.9574470000000002</v>
+        <v>-2.9396264064238</v>
       </c>
       <c r="H31" s="5">
-        <v>-2.2150850000000002</v>
+        <v>-2.2426126747806001</v>
       </c>
       <c r="I31" s="5">
-        <v>-3.0451269999999999</v>
+        <v>-3.0451269136678198</v>
       </c>
       <c r="J31" s="5">
-        <v>-2.0531600000000001</v>
+        <v>-2.0531596193733099</v>
       </c>
       <c r="K31" s="5">
-        <v>-3.095869</v>
+        <v>-3.0958693589168198</v>
       </c>
       <c r="L31" s="5">
-        <v>-2.1112169999999999</v>
+        <v>-2.1112173524889699</v>
       </c>
       <c r="M31" s="5">
         <v>7</v>
@@ -2456,22 +2456,22 @@
         <v>5400</v>
       </c>
       <c r="G32" s="5">
-        <v>-0.69637700000000002</v>
+        <v>-0.69004689993991752</v>
       </c>
       <c r="H32" s="5">
-        <v>-3.6348050000000001</v>
+        <v>-3.6195477376707004</v>
       </c>
       <c r="I32" s="5">
-        <v>-0.49814520000000001</v>
+        <v>-0.49814524947946298</v>
       </c>
       <c r="J32" s="5">
-        <v>-3.5273319999999999</v>
+        <v>-3.5273319093405902</v>
       </c>
       <c r="K32" s="5">
-        <v>-0.55946929999999995</v>
+        <v>-0.55946931958436497</v>
       </c>
       <c r="L32" s="5">
-        <v>-3.5049090000000001</v>
+        <v>-3.5049090535643699</v>
       </c>
       <c r="M32" s="5">
         <v>10</v>
@@ -2506,22 +2506,22 @@
         <v>1650</v>
       </c>
       <c r="G33" s="5">
-        <v>0.27300015</v>
+        <v>0.28604034748183199</v>
       </c>
       <c r="H33" s="5">
-        <v>-1.6549005000000001</v>
+        <v>-1.6738616553310151</v>
       </c>
       <c r="I33" s="5">
-        <v>0.26566394999999998</v>
+        <v>0.26566397279812304</v>
       </c>
       <c r="J33" s="5">
-        <v>-1.6677850000000001</v>
+        <v>-1.6677847105529349</v>
       </c>
       <c r="K33" s="5">
-        <v>0.30046365000000003</v>
+        <v>0.30046365322271196</v>
       </c>
       <c r="L33" s="5">
-        <v>-1.70234</v>
+        <v>-1.70234013012456</v>
       </c>
       <c r="M33" s="5">
         <v>12</v>
@@ -2556,22 +2556,22 @@
         <v>6000</v>
       </c>
       <c r="G34" s="5">
-        <v>-1.2492559999999999</v>
+        <v>-1.2400143763153</v>
       </c>
       <c r="H34" s="5">
-        <v>-2.1959960000000001</v>
+        <v>-2.2118469665819651</v>
       </c>
       <c r="I34" s="5">
-        <v>-0.95277175000000003</v>
+        <v>-0.95277174391218944</v>
       </c>
       <c r="J34" s="5">
-        <v>-2.1301705000000002</v>
+        <v>-2.1301702057408751</v>
       </c>
       <c r="K34" s="5">
-        <v>-0.80554815000000002</v>
+        <v>-0.80554815773930155</v>
       </c>
       <c r="L34" s="5">
-        <v>-2.0600774999999998</v>
+        <v>-2.0600775256103754</v>
       </c>
       <c r="M34" s="5">
         <v>14</v>
@@ -2606,22 +2606,22 @@
         <v>2000</v>
       </c>
       <c r="G35" s="5">
-        <v>0.49404130000000002</v>
+        <v>0.51237810279796203</v>
       </c>
       <c r="H35" s="5">
-        <v>0.45709129999999998</v>
+        <v>0.45189683818661602</v>
       </c>
       <c r="I35" s="5">
-        <v>0.1792386</v>
+        <v>0.17923855694019999</v>
       </c>
       <c r="J35" s="5">
-        <v>0.51083610000000002</v>
+        <v>0.51083614322772197</v>
       </c>
       <c r="K35" s="5">
-        <v>0.64151740000000002</v>
+        <v>0.64151737047778301</v>
       </c>
       <c r="L35" s="5">
-        <v>0.81678110000000004</v>
+        <v>0.81678107287524104</v>
       </c>
       <c r="M35" s="5">
         <v>9</v>
@@ -2656,22 +2656,22 @@
         <v>4000</v>
       </c>
       <c r="G36" s="5">
-        <v>-2.7220200000000001</v>
+        <v>-2.7000099388854499</v>
       </c>
       <c r="H36" s="5">
-        <v>-1.9463029999999999</v>
+        <v>-1.97219322568566</v>
       </c>
       <c r="I36" s="5">
-        <v>-2.7860860000000001</v>
+        <v>-2.78608633190834</v>
       </c>
       <c r="J36" s="5">
-        <v>-1.8381110000000001</v>
+        <v>-1.83811079650181</v>
       </c>
       <c r="K36" s="5">
-        <v>-2.8234159999999999</v>
+        <v>-2.82341606896316</v>
       </c>
       <c r="L36" s="5">
-        <v>-1.774278</v>
+        <v>-1.7742775563802899</v>
       </c>
       <c r="M36" s="5">
         <v>8</v>
@@ -2706,22 +2706,22 @@
         <v>5650</v>
       </c>
       <c r="G37" s="5">
-        <v>0.21568979999999999</v>
+        <v>0.205901841168003</v>
       </c>
       <c r="H37" s="5">
-        <v>-2.486866</v>
+        <v>-2.6222843070308999</v>
       </c>
       <c r="I37" s="5">
-        <v>0.54488970000000003</v>
+        <v>0.54488967728431204</v>
       </c>
       <c r="J37" s="5">
-        <v>-2.688987</v>
+        <v>-2.68898743522755</v>
       </c>
       <c r="K37" s="5">
-        <v>0.2059018</v>
+        <v>0.205901841168003</v>
       </c>
       <c r="L37" s="5">
-        <v>-2.6222840000000001</v>
+        <v>-2.6222843070308999</v>
       </c>
       <c r="M37" s="5">
         <v>12</v>
@@ -2756,22 +2756,22 @@
         <v>8900</v>
       </c>
       <c r="G38" s="5">
-        <v>4.1713699999999996</v>
+        <v>4.1582269929040496</v>
       </c>
       <c r="H38" s="5">
-        <v>2.0801310000000002</v>
+        <v>2.0650714168584501</v>
       </c>
       <c r="I38" s="5">
-        <v>3.8385069999999999</v>
+        <v>3.8385065018784701</v>
       </c>
       <c r="J38" s="5">
-        <v>2.367089</v>
+        <v>2.3670894539220502</v>
       </c>
       <c r="K38" s="5">
-        <v>3.8385069999999999</v>
+        <v>3.8385065018784701</v>
       </c>
       <c r="L38" s="5">
-        <v>2.367089</v>
+        <v>2.3670894539220502</v>
       </c>
       <c r="M38" s="5">
         <v>14</v>
@@ -2806,22 +2806,22 @@
         <v>8900</v>
       </c>
       <c r="G39" s="5">
-        <v>4.3326700000000002</v>
+        <v>4.3072526927375803</v>
       </c>
       <c r="H39" s="5">
-        <v>0.99610180000000004</v>
+        <v>0.98602417930770003</v>
       </c>
       <c r="I39" s="5">
-        <v>4.3652810000000004</v>
+        <v>4.3652811143812702</v>
       </c>
       <c r="J39" s="5">
-        <v>1.428342</v>
+        <v>1.4283424793772499</v>
       </c>
       <c r="K39" s="5">
-        <v>4.3652810000000004</v>
+        <v>4.3652811143812702</v>
       </c>
       <c r="L39" s="5">
-        <v>1.428342</v>
+        <v>1.4283424793772499</v>
       </c>
       <c r="M39" s="5">
         <v>11</v>
@@ -2856,22 +2856,22 @@
         <v>3000</v>
       </c>
       <c r="G40" s="5">
-        <v>-0.62644739999999999</v>
+        <v>-0.61711093830599695</v>
       </c>
       <c r="H40" s="5">
-        <v>-2.0614180000000002</v>
+        <v>-2.0776652323537599</v>
       </c>
       <c r="I40" s="5">
-        <v>-0.28602499999999997</v>
+        <v>-0.28602495565309499</v>
       </c>
       <c r="J40" s="5">
-        <v>-1.864293</v>
+        <v>-1.86429285251557</v>
       </c>
       <c r="K40" s="5">
-        <v>-0.13959289999999999</v>
+        <v>-0.139592949317801</v>
       </c>
       <c r="L40" s="5">
-        <v>-1.8605590000000001</v>
+        <v>-1.8605594786736499</v>
       </c>
       <c r="M40" s="5">
         <v>13</v>
@@ -2906,22 +2906,22 @@
         <v>7700</v>
       </c>
       <c r="G41" s="5">
-        <v>1.421495</v>
+        <v>1.4394379749685899</v>
       </c>
       <c r="H41" s="5">
-        <v>-2.496235</v>
+        <v>-2.5152615919635402</v>
       </c>
       <c r="I41" s="5">
-        <v>0.91432040000000003</v>
+        <v>0.91432040092445999</v>
       </c>
       <c r="J41" s="5">
-        <v>-2.4337029999999999</v>
+        <v>-2.4337034749845499</v>
       </c>
       <c r="K41" s="5">
-        <v>0.18623000000000001</v>
+        <v>0.18622996980908399</v>
       </c>
       <c r="L41" s="5">
-        <v>-2.5422189999999998</v>
+        <v>-2.5422192350043402</v>
       </c>
       <c r="M41" s="5">
         <v>11</v>
@@ -2956,22 +2956,22 @@
         <v>480</v>
       </c>
       <c r="G42" s="5">
-        <v>-1.7033725</v>
+        <v>-1.6949948220623399</v>
       </c>
       <c r="H42" s="5">
-        <v>-0.48704150000000002</v>
+        <v>-0.50716939951094098</v>
       </c>
       <c r="I42" s="5">
-        <v>-1.4288829999999999</v>
+        <v>-1.5619389671181398</v>
       </c>
       <c r="J42" s="5">
-        <v>-8.2468004999999997E-2</v>
+        <v>-0.29481870149815537</v>
       </c>
       <c r="K42" s="5">
-        <v>-1.4288829999999999</v>
+        <v>-1.42888311217394</v>
       </c>
       <c r="L42" s="5">
-        <v>-8.2468004999999997E-2</v>
+        <v>-8.2468003485369798E-2</v>
       </c>
       <c r="M42" s="5">
         <v>10</v>
@@ -3006,22 +3006,22 @@
         <v>800</v>
       </c>
       <c r="G43" s="5">
-        <v>-6.1630919999999999E-2</v>
+        <v>-7.5468454698791695E-2</v>
       </c>
       <c r="H43" s="5">
-        <v>-3.3272439999999999</v>
+        <v>-3.35200688303622</v>
       </c>
       <c r="I43" s="5">
-        <v>-2.1572379999999999E-2</v>
+        <v>-2.15723808368763E-2</v>
       </c>
       <c r="J43" s="5">
-        <v>-3.3314059999999999</v>
+        <v>-3.3314061962677699</v>
       </c>
       <c r="K43" s="5">
-        <v>-0.19498750000000001</v>
+        <v>-0.194987477067186</v>
       </c>
       <c r="L43" s="5">
-        <v>-3.4730059999999998</v>
+        <v>-3.47300561554191</v>
       </c>
       <c r="M43" s="5">
         <v>8</v>
@@ -3056,22 +3056,22 @@
         <v>4000</v>
       </c>
       <c r="G44" s="5">
-        <v>0.14626239999999999</v>
+        <v>0.15637821498871601</v>
       </c>
       <c r="H44" s="5">
-        <v>-1.6415230000000001</v>
+        <v>-1.64824110155249</v>
       </c>
       <c r="I44" s="5">
-        <v>0.34843079999999998</v>
+        <v>0.34843077786554899</v>
       </c>
       <c r="J44" s="5">
-        <v>-1.475786</v>
+        <v>-1.47578553345283</v>
       </c>
       <c r="K44" s="5">
-        <v>-7.9115350000000001E-2</v>
+        <v>-7.9115352568443806E-2</v>
       </c>
       <c r="L44" s="5">
-        <v>-1.687249</v>
+        <v>-1.6872488933696601</v>
       </c>
       <c r="M44" s="5">
         <v>11</v>
@@ -3106,22 +3106,22 @@
         <v>8000</v>
       </c>
       <c r="G45" s="5">
-        <v>1.0096590000000001</v>
+        <v>1.0205470186091601</v>
       </c>
       <c r="H45" s="5">
-        <v>-0.54316019999999998</v>
+        <v>-0.54963550984044796</v>
       </c>
       <c r="I45" s="5">
-        <v>1.3954880000000001</v>
+        <v>1.3954883356993699</v>
       </c>
       <c r="J45" s="5">
-        <v>-0.5422555</v>
+        <v>-0.54225552458910697</v>
       </c>
       <c r="K45" s="5">
-        <v>1.507952</v>
+        <v>1.5079522846715301</v>
       </c>
       <c r="L45" s="5">
-        <v>-0.46530440000000001</v>
+        <v>-0.465304378870675</v>
       </c>
       <c r="M45" s="5">
         <v>14</v>
@@ -3156,22 +3156,22 @@
         <v>3000</v>
       </c>
       <c r="G46" s="5">
-        <v>0.13312060000000001</v>
+        <v>0.117397112573533</v>
       </c>
       <c r="H46" s="5">
-        <v>-4.3595540000000002</v>
+        <v>-4.3790951647976302</v>
       </c>
       <c r="I46" s="5">
-        <v>0.2378149</v>
+        <v>0.23781494702259301</v>
       </c>
       <c r="J46" s="5">
-        <v>-4.3754590000000002</v>
+        <v>-4.3754592482811097</v>
       </c>
       <c r="K46" s="5">
-        <v>0.14706459999999999</v>
+        <v>0.14706459833289601</v>
       </c>
       <c r="L46" s="5">
-        <v>-4.6954950000000002</v>
+        <v>-4.6954945074216203</v>
       </c>
       <c r="M46" s="5">
         <v>13</v>
@@ -3206,22 +3206,22 @@
         <v>4000</v>
       </c>
       <c r="G47" s="5">
-        <v>3.019539</v>
+        <v>3.022496027236365</v>
       </c>
       <c r="H47" s="5">
-        <v>-0.91492525000000002</v>
+        <v>-0.91027672510220703</v>
       </c>
       <c r="I47" s="5">
-        <v>2.649241</v>
+        <v>2.6492407147006451</v>
       </c>
       <c r="J47" s="5">
-        <v>-1.4117375000000001</v>
+        <v>-1.411737376491315</v>
       </c>
       <c r="K47" s="5">
-        <v>2.2515450000000001</v>
+        <v>2.2515453540118253</v>
       </c>
       <c r="L47" s="5">
-        <v>-1.9322195</v>
+        <v>-1.932219436380155</v>
       </c>
       <c r="M47" s="5">
         <v>12</v>
@@ -3256,22 +3256,22 @@
         <v>6000</v>
       </c>
       <c r="G48" s="5">
-        <v>-2.5920420000000002</v>
+        <v>-2.5848715173418149</v>
       </c>
       <c r="H48" s="5">
-        <v>-1.8870795</v>
+        <v>-1.9311176371719752</v>
       </c>
       <c r="I48" s="5">
-        <v>-2.4082664999999999</v>
+        <v>-2.4082666400112651</v>
       </c>
       <c r="J48" s="5">
-        <v>-1.7870705</v>
+        <v>-1.78707048924447</v>
       </c>
       <c r="K48" s="5">
-        <v>-2.2044100000000002</v>
+        <v>-2.20441002297621</v>
       </c>
       <c r="L48" s="5">
-        <v>-1.4849535</v>
+        <v>-1.4849532529988352</v>
       </c>
       <c r="M48" s="5">
         <v>14</v>
@@ -3306,22 +3306,22 @@
         <v>7000</v>
       </c>
       <c r="G49" s="5">
-        <v>0.1437947</v>
+        <v>0.158409756072066</v>
       </c>
       <c r="H49" s="5">
-        <v>-1.5085329999999999</v>
+        <v>-1.5137064730403</v>
       </c>
       <c r="I49" s="5">
-        <v>0.66601750000000004</v>
+        <v>0.66601747435634695</v>
       </c>
       <c r="J49" s="5">
-        <v>-1.4003570000000001</v>
+        <v>-1.4003570546113899</v>
       </c>
       <c r="K49" s="5">
-        <v>1.0829569999999999</v>
+        <v>1.08295652531306</v>
       </c>
       <c r="L49" s="5">
-        <v>-0.76361849999999998</v>
+        <v>-0.76361852911113903</v>
       </c>
       <c r="M49" s="5">
         <v>14</v>
@@ -3356,22 +3356,22 @@
         <v>4000</v>
       </c>
       <c r="G50" s="5">
-        <v>-6.2543970000000004E-2</v>
+        <v>-6.1370866355024201E-2</v>
       </c>
       <c r="H50" s="5">
-        <v>-1.2080690000000001</v>
+        <v>-1.22503578107904</v>
       </c>
       <c r="I50" s="5">
-        <v>0.24862290000000001</v>
+        <v>0.24862292705997799</v>
       </c>
       <c r="J50" s="5">
-        <v>-0.90764940000000005</v>
+        <v>-0.90764935147998105</v>
       </c>
       <c r="K50" s="5">
-        <v>0.10026069999999999</v>
+        <v>0.10026065254901</v>
       </c>
       <c r="L50" s="5">
-        <v>-0.85322469999999995</v>
+        <v>-0.85322467945802805</v>
       </c>
       <c r="M50" s="5">
         <v>11</v>
@@ -3406,22 +3406,22 @@
         <v>2000</v>
       </c>
       <c r="G51" s="5">
-        <v>-2.4642520000000001</v>
+        <v>-2.4593564819234399</v>
       </c>
       <c r="H51" s="5">
-        <v>-1.573647</v>
+        <v>-1.60708744619255</v>
       </c>
       <c r="I51" s="5">
-        <v>-2.2988059999999999</v>
+        <v>-2.2988062985451201</v>
       </c>
       <c r="J51" s="5">
-        <v>-1.5538419999999999</v>
+        <v>-1.55384190173334</v>
       </c>
       <c r="K51" s="5">
-        <v>-2.0587589999999998</v>
+        <v>-2.0587588680697801</v>
       </c>
       <c r="L51" s="5">
-        <v>-0.96391199999999999</v>
+        <v>-0.96391198502973097</v>
       </c>
       <c r="M51" s="5">
         <v>11</v>
@@ -3456,22 +3456,22 @@
         <v>3000</v>
       </c>
       <c r="G52" s="5">
-        <v>-2.1538620000000002</v>
+        <v>-2.1482734624019701</v>
       </c>
       <c r="H52" s="5">
-        <v>-1.745088</v>
+        <v>-1.77840905167689</v>
       </c>
       <c r="I52" s="5">
-        <v>-2.1133850000000001</v>
+        <v>-2.1133850003132002</v>
       </c>
       <c r="J52" s="5">
-        <v>-1.6636709999999999</v>
+        <v>-1.66367083158906</v>
       </c>
       <c r="K52" s="5">
-        <v>-1.4790989999999999</v>
+        <v>-1.47909888215028</v>
       </c>
       <c r="L52" s="5">
-        <v>-1.3006420000000001</v>
+        <v>-1.3006418720347099</v>
       </c>
       <c r="M52" s="5">
         <v>11</v>
@@ -3506,22 +3506,22 @@
         <v>2830</v>
       </c>
       <c r="G53" s="5">
-        <v>-4.5199740000000004</v>
+        <v>-4.5062835801788497</v>
       </c>
       <c r="H53" s="5">
-        <v>-1.2923199999999999</v>
+        <v>-1.32099210070395</v>
       </c>
       <c r="I53" s="5">
-        <v>-4.4720409999999999</v>
+        <v>-4.4720405763146296</v>
       </c>
       <c r="J53" s="5">
-        <v>-1.0450680000000001</v>
+        <v>-1.04506812597035</v>
       </c>
       <c r="K53" s="5">
-        <v>-4.4720409999999999</v>
+        <v>-4.4720405763146296</v>
       </c>
       <c r="L53" s="5">
-        <v>-1.0450680000000001</v>
+        <v>-1.04506812597035</v>
       </c>
       <c r="M53" s="5">
         <v>7</v>
@@ -3556,22 +3556,22 @@
         <v>1650</v>
       </c>
       <c r="G54" s="5">
-        <v>0.38857900000000001</v>
+        <v>0.40527697630687298</v>
       </c>
       <c r="H54" s="5">
-        <v>-1.708412</v>
+        <v>-1.71568520285205</v>
       </c>
       <c r="I54" s="5">
-        <v>0.43427500000000002</v>
+        <v>0.43427499983134998</v>
       </c>
       <c r="J54" s="5">
-        <v>-1.6103419999999999</v>
+        <v>-1.61034174268549</v>
       </c>
       <c r="K54" s="5">
-        <v>0.42169610000000002</v>
+        <v>0.42169610427047299</v>
       </c>
       <c r="L54" s="5">
-        <v>-1.3692770000000001</v>
+        <v>-1.36927747888658</v>
       </c>
       <c r="M54" s="5">
         <v>12</v>
@@ -3606,22 +3606,22 @@
         <v>2500</v>
       </c>
       <c r="G55" s="5">
-        <v>2.0476489999999998</v>
+        <v>2.0432618921043098</v>
       </c>
       <c r="H55" s="5">
-        <v>-2.6618469999999999</v>
+        <v>-2.6394391337257153</v>
       </c>
       <c r="I55" s="5">
-        <v>2.1491259999999999</v>
+        <v>2.1491264040238902</v>
       </c>
       <c r="J55" s="5">
-        <v>-2.5713689999999998</v>
+        <v>-2.5713691978540698</v>
       </c>
       <c r="K55" s="5">
-        <v>2.1698050000000002</v>
+        <v>2.1698050210341102</v>
       </c>
       <c r="L55" s="5">
-        <v>-2.4818929999999999</v>
+        <v>-2.4818932163173901</v>
       </c>
       <c r="M55" s="5">
         <v>18</v>
